--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualInventoryDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="虚拟仓差异" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>SKU</t>
   </si>
@@ -36,64 +36,103 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>实体仓名称</t>
+  </si>
+  <si>
+    <t>实体仓实际库存</t>
+  </si>
+  <si>
+    <t>实体仓可用</t>
+  </si>
+  <si>
+    <t>实体仓冻结</t>
+  </si>
+  <si>
+    <t>实体仓在途</t>
+  </si>
+  <si>
+    <t>实体仓待检</t>
+  </si>
+  <si>
+    <t>实体仓已分配数</t>
+  </si>
+  <si>
+    <t>实体仓未分配数</t>
+  </si>
+  <si>
+    <t>库存差异</t>
+  </si>
+  <si>
+    <t>虚拟仓编号</t>
+  </si>
+  <si>
+    <t>虚拟仓</t>
+  </si>
+  <si>
+    <t>虚拟仓库存</t>
+  </si>
+  <si>
+    <t>虚拟仓可用库存</t>
+  </si>
+  <si>
+    <t>虚拟仓冻结库存</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.realQty}</t>
+  </si>
+  <si>
+    <t>{.usableQty}</t>
+  </si>
+  <si>
+    <t>{.frozenQty}</t>
+  </si>
+  <si>
+    <t>{.inTransitQty}</t>
+  </si>
+  <si>
+    <t>{.waitQcQty}</t>
+  </si>
+  <si>
+    <t>{.distributionQty}</t>
+  </si>
+  <si>
+    <t>{.unDistributionQty}</t>
+  </si>
+  <si>
+    <t>{.isDiff}</t>
+  </si>
+  <si>
+    <t>{.virtualWarehouseCode}</t>
+  </si>
+  <si>
+    <t>{.virtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.virtualQty}</t>
+  </si>
+  <si>
+    <t>{.virtualUsableQty}</t>
+  </si>
+  <si>
+    <t>{.virtualFrozenQty}</t>
+  </si>
+  <si>
+    <t>实体仓编号</t>
+  </si>
+  <si>
     <t>实体仓可用库存</t>
   </si>
   <si>
-    <t>实体仓已分配数</t>
-  </si>
-  <si>
-    <t>实体仓未分配数</t>
-  </si>
-  <si>
-    <t>虚拟仓</t>
-  </si>
-  <si>
-    <t>虚拟仓库存</t>
-  </si>
-  <si>
-    <t>虚拟仓可用库存</t>
-  </si>
-  <si>
-    <t>虚拟仓冻结库存</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.usableQty}</t>
-  </si>
-  <si>
-    <t>{.distributionQty}</t>
-  </si>
-  <si>
-    <t>{.unDistributionQty}</t>
-  </si>
-  <si>
-    <t>{.virtualWarehouseName}</t>
-  </si>
-  <si>
-    <t>{.virtualQty}</t>
-  </si>
-  <si>
-    <t>{.virtualUsableQty}</t>
-  </si>
-  <si>
-    <t>{.virtualFrozenQty}</t>
-  </si>
-  <si>
-    <t>实体仓编号</t>
-  </si>
-  <si>
-    <t>实体仓名称</t>
-  </si>
-  <si>
     <t>{.warehouseCode}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
   </si>
 </sst>
 </file>
@@ -1061,21 +1100,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.25" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="21.875" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="15.875" customWidth="1"/>
+    <col min="2" max="4" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
+    <col min="6" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="16.5" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1091,46 +1132,88 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1163,42 +1246,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualInventoryDiff.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="虚拟仓差异" sheetId="1" r:id="rId1"/>
-    <sheet name="实体仓库分配统计" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>SKU</t>
   </si>
@@ -108,7 +107,7 @@
     <t>{.unDistributionQty}</t>
   </si>
   <si>
-    <t>{.isDiff}</t>
+    <t>{.isDiffName}</t>
   </si>
   <si>
     <t>{.virtualWarehouseCode}</t>
@@ -124,15 +123,6 @@
   </si>
   <si>
     <t>{.virtualFrozenQty}</t>
-  </si>
-  <si>
-    <t>实体仓编号</t>
-  </si>
-  <si>
-    <t>实体仓可用库存</t>
-  </si>
-  <si>
-    <t>{.warehouseCode}</t>
   </si>
 </sst>
 </file>
@@ -1221,71 +1211,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="14.75" customWidth="1"/>
-    <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="20.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualInventoryDiff.xlsx
@@ -65,7 +65,7 @@
     <t>虚拟仓编号</t>
   </si>
   <si>
-    <t>虚拟仓</t>
+    <t>虚拟仓名称</t>
   </si>
   <si>
     <t>虚拟仓库存</t>
